--- a/artfynd/A 25284-2025 artfynd.xlsx
+++ b/artfynd/A 25284-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89709447</v>
+        <v>114558654</v>
       </c>
       <c r="B2" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224363</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövsta lund O 240 m, Ög</t>
+          <t>Vistingegölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555285.6477288723</v>
+        <v>555004</v>
       </c>
       <c r="R2" t="n">
-        <v>6506686.4878874</v>
+        <v>6506460</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-12-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-12-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I kanten av granskogen utanför inventeringsområdet. Ser dock ut som produktionsskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,27 +759,128 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Alexander Nordstrand</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>EWN0114 Vistinge NVI 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>89709447</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lövsta lund O 240 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>555286</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6506686</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-12-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-12-19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Mirjam Ideström</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Mirjam Ideström, Jan-Erik Axelsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25284-2025 artfynd.xlsx
+++ b/artfynd/A 25284-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>EWN0114 Vistinge NVI 2023</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114558654</t>
         </is>
       </c>
     </row>
@@ -881,8 +891,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89709447</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25284-2025 artfynd.xlsx
+++ b/artfynd/A 25284-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114558654</v>
+        <v>135688453</v>
       </c>
       <c r="B2" t="n">
-        <v>93233</v>
+        <v>107871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vistingegölen, Ög</t>
+          <t>Lövsta lund 270 m O, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555004</v>
+        <v>555309</v>
       </c>
       <c r="R2" t="n">
-        <v>6506460</v>
+        <v>6506720</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +753,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I kanten av granskogen utanför inventeringsområdet. Ser dock ut som produktionsskog.</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,75 +777,77 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gräsbevuxen vägkant</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Nordstrand</t>
+          <t>Göran Göransson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Julia Svensson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>EWN0114 Vistinge NVI 2023</t>
-        </is>
-      </c>
+          <t>Göran Göransson, Göran Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114558654</t>
+          <t>https://artportalen.se/Sighting/135688453</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89709447</v>
+        <v>114558654</v>
       </c>
       <c r="B3" t="n">
-        <v>97985</v>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224363</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövsta lund O 240 m, Ög</t>
+          <t>Vistingegölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555286</v>
+        <v>555004</v>
       </c>
       <c r="R3" t="n">
-        <v>6506686</v>
+        <v>6506460</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +871,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-12-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-12-19</t>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I kanten av granskogen utanför inventeringsområdet. Ser dock ut som produktionsskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,28 +890,134 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Alexander Nordstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>EWN0114 Vistinge NVI 2023</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114558654</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>89709447</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lövsta lund O 240 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>555286</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6506686</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-12-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-12-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Mirjam Ideström</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Mirjam Ideström, Jan-Erik Axelsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89709447</t>
         </is>
@@ -901,6 +1027,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25284-2025 artfynd.xlsx
+++ b/artfynd/A 25284-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114558654</v>
+        <v>135688453</v>
       </c>
       <c r="B2" t="n">
-        <v>93233</v>
+        <v>107876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vistingegölen, Ög</t>
+          <t>Lövsta lund 270 m O, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555004</v>
+        <v>555309</v>
       </c>
       <c r="R2" t="n">
-        <v>6506460</v>
+        <v>6506720</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +753,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I kanten av granskogen utanför inventeringsområdet. Ser dock ut som produktionsskog.</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,75 +777,77 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gräsbevuxen vägkant</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Nordstrand</t>
+          <t>Göran Göransson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Julia Svensson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>EWN0114 Vistinge NVI 2023</t>
-        </is>
-      </c>
+          <t>Göran Göransson, Göran Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114558654</t>
+          <t>https://artportalen.se/Sighting/135688453</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89709447</v>
+        <v>114558654</v>
       </c>
       <c r="B3" t="n">
-        <v>97985</v>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224363</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövsta lund O 240 m, Ög</t>
+          <t>Vistingegölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555286</v>
+        <v>555004</v>
       </c>
       <c r="R3" t="n">
-        <v>6506686</v>
+        <v>6506460</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +871,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-12-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-12-19</t>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I kanten av granskogen utanför inventeringsområdet. Ser dock ut som produktionsskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,28 +890,134 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Alexander Nordstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>EWN0114 Vistinge NVI 2023</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114558654</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>89709447</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lövsta lund O 240 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>555286</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6506686</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-12-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-12-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Mirjam Ideström</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Mirjam Ideström, Jan-Erik Axelsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89709447</t>
         </is>
@@ -901,6 +1027,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25284-2025 artfynd.xlsx
+++ b/artfynd/A 25284-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135688453</v>
       </c>
       <c r="B2" t="n">
-        <v>107876</v>
+        <v>107878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25284-2025 artfynd.xlsx
+++ b/artfynd/A 25284-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135688453</v>
       </c>
       <c r="B2" t="n">
-        <v>107878</v>
+        <v>107901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25284-2025 artfynd.xlsx
+++ b/artfynd/A 25284-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135688453</v>
       </c>
       <c r="B2" t="n">
-        <v>107901</v>
+        <v>107903</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25284-2025 artfynd.xlsx
+++ b/artfynd/A 25284-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135688453</v>
       </c>
       <c r="B2" t="n">
-        <v>107903</v>
+        <v>107904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25284-2025 artfynd.xlsx
+++ b/artfynd/A 25284-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135688453</v>
       </c>
       <c r="B2" t="n">
-        <v>107904</v>
+        <v>107905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25284-2025 artfynd.xlsx
+++ b/artfynd/A 25284-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135688453</v>
       </c>
       <c r="B2" t="n">
-        <v>107905</v>
+        <v>107911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25284-2025 artfynd.xlsx
+++ b/artfynd/A 25284-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135688453</v>
       </c>
       <c r="B2" t="n">
-        <v>107911</v>
+        <v>107912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
